--- a/examples/output/MNL_modeChoice_RP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_RP_WTP.xlsx
@@ -446,25 +446,25 @@
         <v>8</v>
       </c>
       <c r="B2">
-        <v>0.6093287523842155</v>
+        <v>0.6093287523839462</v>
       </c>
       <c r="C2">
-        <v>0.18874389349741216</v>
+        <v>0.1887438934974606</v>
       </c>
       <c r="D2">
-        <v>3.228336244915759</v>
+        <v>3.228336244913504</v>
       </c>
       <c r="E2">
-        <v>0.0012451252414447112</v>
+        <v>0.0012451252414544811</v>
       </c>
       <c r="F2">
-        <v>0.18794420729071754</v>
+        <v>0.18794420729077574</v>
       </c>
       <c r="G2">
-        <v>3.242072534013715</v>
+        <v>3.242072534011278</v>
       </c>
       <c r="H2">
-        <v>0.0011866381659064729</v>
+        <v>0.001186638165916687</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -472,25 +472,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0.26058639294994557</v>
+        <v>0.2605863929499275</v>
       </c>
       <c r="C3">
-        <v>0.07780445605623351</v>
+        <v>0.07780445605624886</v>
       </c>
       <c r="D3">
-        <v>3.3492476672750673</v>
+        <v>3.3492476672741747</v>
       </c>
       <c r="E3">
-        <v>0.0008103132736096974</v>
+        <v>0.0008103132736123619</v>
       </c>
       <c r="F3">
-        <v>0.07650354268588301</v>
+        <v>0.07650354268589855</v>
       </c>
       <c r="G3">
-        <v>3.4062003379358647</v>
+        <v>3.406200337934937</v>
       </c>
       <c r="H3">
-        <v>0.0006587382150240462</v>
+        <v>0.0006587382150262666</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -498,25 +498,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0.10740443300447526</v>
+        <v>0.10740443300448461</v>
       </c>
       <c r="C4">
-        <v>0.04506437715133213</v>
+        <v>0.045064377151342275</v>
       </c>
       <c r="D4">
-        <v>2.3833555414245935</v>
+        <v>2.3833555414242644</v>
       </c>
       <c r="E4">
-        <v>0.01715561623481987</v>
+        <v>0.01715561623483519</v>
       </c>
       <c r="F4">
-        <v>0.04520626767764363</v>
+        <v>0.04520626767765426</v>
       </c>
       <c r="G4">
-        <v>2.3758748182962957</v>
+        <v>2.375874818295944</v>
       </c>
       <c r="H4">
-        <v>0.017507401187205396</v>
+        <v>0.01750740118722205</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -524,25 +524,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.33108363069860286</v>
+        <v>0.3310836306990152</v>
       </c>
       <c r="C5">
-        <v>0.12797716669505255</v>
+        <v>0.1279771666950962</v>
       </c>
       <c r="D5">
-        <v>2.5870523566717014</v>
+        <v>2.587052356674041</v>
       </c>
       <c r="E5">
-        <v>0.009680088226917016</v>
+        <v>0.009680088226851291</v>
       </c>
       <c r="F5">
-        <v>0.1279884858878155</v>
+        <v>0.12798848588786407</v>
       </c>
       <c r="G5">
-        <v>2.5868235599630762</v>
+        <v>2.586823559965316</v>
       </c>
       <c r="H5">
-        <v>0.009686517866817956</v>
+        <v>0.009686517866754896</v>
       </c>
     </row>
   </sheetData>

--- a/examples/output/MNL_modeChoice_RP_WTP.xlsx
+++ b/examples/output/MNL_modeChoice_RP_WTP.xlsx
@@ -449,22 +449,22 @@
         <v>0.6093287523839462</v>
       </c>
       <c r="C2">
-        <v>0.1887438934974606</v>
+        <v>0.18874389349746307</v>
       </c>
       <c r="D2">
-        <v>3.228336244913504</v>
+        <v>3.2283362449134616</v>
       </c>
       <c r="E2">
-        <v>0.0012451252414544811</v>
+        <v>0.0012451252414547032</v>
       </c>
       <c r="F2">
-        <v>0.18794420729077574</v>
+        <v>0.18794420729078</v>
       </c>
       <c r="G2">
-        <v>3.242072534011278</v>
+        <v>3.2420725340112044</v>
       </c>
       <c r="H2">
-        <v>0.001186638165916687</v>
+        <v>0.001186638165917131</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -472,25 +472,25 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>0.2605863929499275</v>
+        <v>0.2605863929499284</v>
       </c>
       <c r="C3">
-        <v>0.07780445605624886</v>
+        <v>0.07780445605625262</v>
       </c>
       <c r="D3">
-        <v>3.3492476672741747</v>
+        <v>3.349247667274024</v>
       </c>
       <c r="E3">
-        <v>0.0008103132736123619</v>
+        <v>0.000810313273612806</v>
       </c>
       <c r="F3">
-        <v>0.07650354268589855</v>
+        <v>0.07650354268590519</v>
       </c>
       <c r="G3">
-        <v>3.406200337934937</v>
+        <v>3.4062003379346533</v>
       </c>
       <c r="H3">
-        <v>0.0006587382150262666</v>
+        <v>0.0006587382150269327</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -498,25 +498,25 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>0.10740443300448461</v>
+        <v>0.10740443300448498</v>
       </c>
       <c r="C4">
-        <v>0.045064377151342275</v>
+        <v>0.04506437715134269</v>
       </c>
       <c r="D4">
-        <v>2.3833555414242644</v>
+        <v>2.38335554142425</v>
       </c>
       <c r="E4">
-        <v>0.01715561623483519</v>
+        <v>0.017155616234835858</v>
       </c>
       <c r="F4">
-        <v>0.04520626767765426</v>
+        <v>0.045206267677655204</v>
       </c>
       <c r="G4">
-        <v>2.375874818295944</v>
+        <v>2.375874818295902</v>
       </c>
       <c r="H4">
-        <v>0.01750740118722205</v>
+        <v>0.017507401187224048</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -524,25 +524,25 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.3310836306990152</v>
+        <v>0.33108363069901475</v>
       </c>
       <c r="C5">
-        <v>0.1279771666950962</v>
+        <v>0.12797716669509598</v>
       </c>
       <c r="D5">
-        <v>2.587052356674041</v>
+        <v>2.5870523566740418</v>
       </c>
       <c r="E5">
         <v>0.009680088226851291</v>
       </c>
       <c r="F5">
-        <v>0.12798848588786407</v>
+        <v>0.12798848588786496</v>
       </c>
       <c r="G5">
-        <v>2.586823559965316</v>
+        <v>2.586823559965295</v>
       </c>
       <c r="H5">
-        <v>0.009686517866754896</v>
+        <v>0.009686517866755562</v>
       </c>
     </row>
   </sheetData>
